--- a/04_Figures/F04_association/modules/T2/wilcoxon/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/T2/wilcoxon/c_data/results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -64,12 +64,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -468,14 +462,14 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0109895071469866</v>
+        <v>-0.0281308504876008</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="n">
-        <v>0.778865578865579</v>
+        <v>0.694327894327894</v>
       </c>
       <c r="G2" t="n">
-        <v>0.920477502295684</v>
+        <v>0.763760683760684</v>
       </c>
     </row>
     <row r="3">
@@ -489,14 +483,14 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00978028380712953</v>
+        <v>0.0545531414531688</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="n">
-        <v>0.955089355089355</v>
+        <v>0.120590520590521</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.615384615384616</v>
       </c>
     </row>
     <row r="4">
@@ -510,14 +504,14 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0500149754623554</v>
+        <v>0.0437204344434727</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="n">
-        <v>0.280963480963481</v>
+        <v>0.231857031857032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.608754208754209</v>
+        <v>0.615384615384616</v>
       </c>
     </row>
     <row r="5">
@@ -531,14 +525,14 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0742406474776733</v>
+        <v>-0.090672674901554</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="n">
-        <v>0.0938616938616939</v>
+        <v>0.535819735819736</v>
       </c>
       <c r="G5" t="n">
-        <v>0.608754208754209</v>
+        <v>0.763760683760684</v>
       </c>
     </row>
     <row r="6">
@@ -552,14 +546,14 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.101739458824472</v>
+        <v>-0.111609693266616</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="n">
-        <v>0.280963480963481</v>
+        <v>0.335664335664336</v>
       </c>
       <c r="G6" t="n">
-        <v>0.608754208754209</v>
+        <v>0.615384615384616</v>
       </c>
     </row>
     <row r="7">
@@ -573,14 +567,14 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.208630645705653</v>
+        <v>-0.015436120485889</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="n">
-        <v>0.189277389277389</v>
+        <v>0.694327894327894</v>
       </c>
       <c r="G7" t="n">
-        <v>0.608754208754209</v>
+        <v>0.763760683760684</v>
       </c>
     </row>
     <row r="8">
@@ -594,14 +588,14 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0154823015656248</v>
+        <v>0.019690928559502</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="n">
-        <v>0.612587412587413</v>
+        <v>0.778865578865579</v>
       </c>
       <c r="G8" t="n">
-        <v>0.902626262626263</v>
+        <v>0.778865578865579</v>
       </c>
     </row>
     <row r="9">
@@ -615,14 +609,14 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0425526659372732</v>
+        <v>0.0586354000689937</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="n">
-        <v>0.694327894327894</v>
+        <v>0.280963480963481</v>
       </c>
       <c r="G9" t="n">
-        <v>0.902626262626263</v>
+        <v>0.615384615384616</v>
       </c>
     </row>
     <row r="10">
@@ -636,14 +630,14 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.100737127631935</v>
+        <v>0.0566122472545513</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="n">
-        <v>0.396891996891997</v>
+        <v>0.231857031857032</v>
       </c>
       <c r="G10" t="n">
-        <v>0.737085137085137</v>
+        <v>0.615384615384616</v>
       </c>
     </row>
     <row r="11">
@@ -657,14 +651,14 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0613669276066202</v>
+        <v>-0.162067671130595</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="n">
-        <v>0.280963480963481</v>
+        <v>0.694327894327894</v>
       </c>
       <c r="G11" t="n">
-        <v>0.608754208754209</v>
+        <v>0.763760683760684</v>
       </c>
     </row>
     <row r="12">
@@ -678,56 +672,14 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.106359815541511</v>
+        <v>-0.0855325167499414</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.231857031857032</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.170661627630581</v>
-      </c>
-      <c r="E13"/>
-      <c r="F13" t="n">
-        <v>0.694327894327894</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.902626262626263</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0862000986578403</v>
-      </c>
-      <c r="E14"/>
-      <c r="F14" t="n">
-        <v>0.231857031857032</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.608754208754209</v>
+        <v>0.615384615384616</v>
       </c>
     </row>
   </sheetData>
@@ -743,45 +695,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" t="s">
-        <v>23</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>25</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -790,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0742406474776733</v>
+        <v>0.0566122472545513</v>
       </c>
     </row>
   </sheetData>
